--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486495_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486495_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.3741</v>
+        <v>7.3605</v>
       </c>
       <c r="E2" t="n">
-        <v>6.8866</v>
+        <v>5.6572</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4875</v>
+        <v>1.7032</v>
       </c>
       <c r="G2" t="n">
         <v>0.1493</v>
@@ -610,13 +610,13 @@
         <v>1.9576</v>
       </c>
       <c r="S2" t="n">
-        <v>2.6205</v>
+        <v>1.607</v>
       </c>
       <c r="T2" t="n">
-        <v>2.5368</v>
+        <v>1.3075</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0837</v>
+        <v>0.2995</v>
       </c>
       <c r="V2" t="n">
         <v>3.6467</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.6188</v>
+        <v>5.9213</v>
       </c>
       <c r="E3" t="n">
-        <v>5.1211</v>
+        <v>6.2387</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5023</v>
+        <v>-0.3174</v>
       </c>
       <c r="G3" t="n">
         <v>3.5368</v>
@@ -688,13 +688,13 @@
         <v>1.5225</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6782</v>
+        <v>0.6243</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8099</v>
+        <v>0.3076</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1317</v>
+        <v>0.3166</v>
       </c>
       <c r="V3" t="n">
         <v>1.3252</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.9246</v>
+        <v>3.782</v>
       </c>
       <c r="E4" t="n">
-        <v>1.83</v>
+        <v>1.7182</v>
       </c>
       <c r="F4" t="n">
-        <v>2.0946</v>
+        <v>2.0638</v>
       </c>
       <c r="G4" t="n">
         <v>3.2464</v>
@@ -766,13 +766,13 @@
         <v>0.87</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7005</v>
+        <v>0.5579</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4831</v>
+        <v>0.3713</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2174</v>
+        <v>0.1866</v>
       </c>
       <c r="V4" t="n">
         <v>0.1952</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.8518</v>
+        <v>2.5744</v>
       </c>
       <c r="E5" t="n">
         <v>2.2426</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6093</v>
+        <v>0.3318</v>
       </c>
       <c r="G5" t="n">
         <v>2.7971</v>
@@ -844,13 +844,13 @@
         <v>1.7401</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3821</v>
+        <v>1.1047</v>
       </c>
       <c r="T5" t="n">
         <v>0.4951</v>
       </c>
       <c r="U5" t="n">
-        <v>0.887</v>
+        <v>0.6096</v>
       </c>
       <c r="V5" t="n">
         <v>0.1952</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.2986</v>
+        <v>1.4547</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0194</v>
+        <v>1.2371</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2792</v>
+        <v>0.2176</v>
       </c>
       <c r="G6" t="n">
         <v>-0.7774</v>
@@ -922,13 +922,13 @@
         <v>1.9576</v>
       </c>
       <c r="S6" t="n">
-        <v>2.319</v>
+        <v>1.4751</v>
       </c>
       <c r="T6" t="n">
-        <v>1.7797</v>
+        <v>0.9974</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5393</v>
+        <v>0.4777</v>
       </c>
       <c r="V6" t="n">
         <v>-0.113</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6519</v>
+        <v>1.413</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.604</v>
+        <v>-0.3805</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2559</v>
+        <v>1.7936</v>
       </c>
       <c r="G7" t="n">
         <v>-1.0506</v>
@@ -1000,13 +1000,13 @@
         <v>1.0875</v>
       </c>
       <c r="S7" t="n">
-        <v>1.5328</v>
+        <v>1.2939</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4266</v>
+        <v>0.6501</v>
       </c>
       <c r="U7" t="n">
-        <v>1.1061</v>
+        <v>0.6438</v>
       </c>
       <c r="V7" t="n">
         <v>0.0822</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.172</v>
+        <v>0.2327</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.8654</v>
+        <v>-1.3066</v>
       </c>
       <c r="F8" t="n">
-        <v>1.6934</v>
+        <v>1.5393</v>
       </c>
       <c r="G8" t="n">
         <v>-0.1137</v>
@@ -1078,13 +1078,13 @@
         <v>1.0875</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0583</v>
+        <v>0.3464</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.1947</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6952</v>
+        <v>0.5411</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. PARRADO CALABRIA</t>
+          <t>R. SEOANE RODICIO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2743</v>
+        <v>-1.09</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1255</v>
+        <v>-0.2045</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1488</v>
+        <v>-0.8856000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7045</v>
+        <v>-2.5668</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.1435</v>
+        <v>-1.609</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4391</v>
+        <v>-0.9578</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.0486</v>
+        <v>-1.0781</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.1251</v>
+        <v>-1.3076</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0765</v>
+        <v>0.2295</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3442</v>
+        <v>-1.4887</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0184</v>
+        <v>-0.3013</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3626</v>
+        <v>-1.1873</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.435</v>
+        <v>1.7401</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6525</v>
+        <v>1.7401</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9951</v>
+        <v>0.9797</v>
       </c>
       <c r="T9" t="n">
-        <v>1.0106</v>
+        <v>0.8736</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0155</v>
+        <v>0.106</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.13</v>
+        <v>-1.243</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.13</v>
+        <v>-1.243</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. SEOANE RODICIO</t>
+          <t>G. JOFRESA SARRET</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7528</v>
+        <v>-1.7923</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6515</v>
+        <v>-0.7118</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1013</v>
+        <v>-1.0805</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.5668</v>
+        <v>-0.4337</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.609</v>
+        <v>-0.0122</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9578</v>
+        <v>-0.4215</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.0781</v>
+        <v>0.6317</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.3076</v>
+        <v>0.0547</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2295</v>
+        <v>0.577</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.4887</v>
+        <v>-1.0654</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3013</v>
+        <v>-0.067</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.1873</v>
+        <v>-0.9985000000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>1.7401</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R10" t="n">
-        <v>1.7401</v>
+        <v>1.0875</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3169</v>
+        <v>-0.0333</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4266</v>
+        <v>-0.256</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1097</v>
+        <v>0.2226</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.243</v>
+        <v>-1.3252</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.243</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. JOFRESA SARRET</t>
+          <t>M. NUGU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.1082</v>
+        <v>-1.959</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9353</v>
+        <v>-2.4275</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.173</v>
+        <v>0.4686</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.4337</v>
+        <v>-0.1506</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.0122</v>
+        <v>0.4415</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4215</v>
+        <v>-0.5921</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6317</v>
+        <v>-0.1904</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0547</v>
+        <v>-0.0207</v>
       </c>
       <c r="L11" t="n">
-        <v>0.577</v>
+        <v>-0.1697</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.0654</v>
+        <v>0.0398</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.067</v>
+        <v>0.4621</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9985000000000001</v>
+        <v>-0.4224</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R11" t="n">
-        <v>1.0875</v>
+        <v>1.9576</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3493</v>
+        <v>1.1518</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4795</v>
+        <v>0.3076</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1301</v>
+        <v>0.8442</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.3252</v>
+        <v>-2.7427</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-0.3698</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.3252</v>
+        <v>-2.3729</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. ALONSO CUEVAS</t>
+          <t>A. PARRADO CALABRIA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,40 +1345,40 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.2539</v>
+        <v>-2.0258</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.1506</v>
+        <v>-1.9078</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1033</v>
+        <v>-0.118</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.5175</v>
+        <v>-0.7045</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3437</v>
+        <v>-1.1435</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.1738</v>
+        <v>0.4391</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.6521</v>
+        <v>-1.0486</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0547</v>
+        <v>-1.1251</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.7068</v>
+        <v>0.0765</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.8653999999999999</v>
+        <v>0.3442</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.3985</v>
+        <v>-0.0184</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.467</v>
+        <v>0.3626</v>
       </c>
       <c r="P12" t="n">
         <v>-0.435</v>
@@ -1390,28 +1390,28 @@
         <v>0.6525</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3014</v>
+        <v>0.2436</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.411</v>
+        <v>0.2283</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1096</v>
+        <v>0.0153</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. NUGU</t>
+          <t>A. ALONSO CUEVAS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.3674</v>
+        <v>-2.0805</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.6511</v>
+        <v>-2.0388</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2836</v>
+        <v>-0.0417</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.1506</v>
+        <v>-1.5175</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4415</v>
+        <v>-0.3437</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5921</v>
+        <v>-1.1738</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.1904</v>
+        <v>-0.6521</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.0207</v>
+        <v>0.0547</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.1697</v>
+        <v>-0.7068</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0398</v>
+        <v>-0.8653999999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>0.4621</v>
+        <v>-0.3985</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.4224</v>
+        <v>-0.467</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.2175</v>
+        <v>-0.435</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R13" t="n">
-        <v>1.9576</v>
+        <v>0.6525</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7433999999999999</v>
+        <v>-0.128</v>
       </c>
       <c r="T13" t="n">
-        <v>0.08409999999999999</v>
+        <v>-0.2992</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6592</v>
+        <v>0.1712</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.7427</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.3698</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.3729</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1501,28 +1501,28 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>13.7912</v>
+        <v>13.791</v>
       </c>
       <c r="E14" t="n">
-        <v>8.116300000000003</v>
+        <v>8.116299999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>5.674799999999999</v>
+        <v>5.674700000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>2.414799999999999</v>
+        <v>2.4148</v>
       </c>
       <c r="H14" t="n">
         <v>1.2474</v>
       </c>
       <c r="I14" t="n">
-        <v>1.167500000000001</v>
+        <v>1.1675</v>
       </c>
       <c r="J14" t="n">
-        <v>7.491799999999999</v>
+        <v>7.4918</v>
       </c>
       <c r="K14" t="n">
-        <v>2.8459</v>
+        <v>2.845899999999999</v>
       </c>
       <c r="L14" t="n">
         <v>4.645799999999999</v>
@@ -1549,13 +1549,13 @@
         <v>9.223100000000002</v>
       </c>
       <c r="T14" t="n">
-        <v>4.7887</v>
+        <v>4.7886</v>
       </c>
       <c r="U14" t="n">
-        <v>4.4341</v>
+        <v>4.4342</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.109400000000001</v>
+        <v>-1.1094</v>
       </c>
       <c r="W14" t="n">
         <v>8.885899999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.1553</v>
+        <v>1.8291</v>
       </c>
       <c r="E15" t="n">
-        <v>1.1091</v>
+        <v>0.8856000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0461</v>
+        <v>0.9435</v>
       </c>
       <c r="G15" t="n">
         <v>2.7665</v>
@@ -1624,13 +1624,13 @@
         <v>1.9576</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3513</v>
+        <v>-0.6775</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2019</v>
+        <v>-0.4254</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1494</v>
+        <v>-0.2521</v>
       </c>
       <c r="V15" t="n">
         <v>-1.13</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. KANDE KIELI</t>
+          <t>M. LAPORNIK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3232</v>
+        <v>0.3461</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7104</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0336</v>
+        <v>0.2523</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6556</v>
+        <v>-1.0596</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4197</v>
+        <v>0.4408</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2359</v>
+        <v>-1.5005</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7633</v>
+        <v>0.63</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5721000000000001</v>
+        <v>1.3901</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1912</v>
+        <v>-0.7601</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1077</v>
+        <v>-1.6896</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1523</v>
+        <v>-0.9493</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0446</v>
+        <v>-0.7403</v>
       </c>
       <c r="P16" t="n">
-        <v>1.9576</v>
+        <v>1.0875</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9576</v>
+        <v>2.1751</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4812</v>
+        <v>-1.007</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0529</v>
+        <v>-0.7739</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4283</v>
+        <v>-0.2331</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.4552</v>
+        <v>1.3252</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.3252</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.4552</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. LAPORNIK</t>
+          <t>J. POWELL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6198</v>
+        <v>-0.2674</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3533</v>
+        <v>-0.0145</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2665</v>
+        <v>-0.2528</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.0596</v>
+        <v>0.9295</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4408</v>
+        <v>-0.5383</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.5005</v>
+        <v>1.4678</v>
       </c>
       <c r="J17" t="n">
-        <v>0.63</v>
+        <v>1.8397</v>
       </c>
       <c r="K17" t="n">
-        <v>1.3901</v>
+        <v>-0.3039</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.7601</v>
+        <v>2.1436</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.6896</v>
+        <v>-0.9101</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9493</v>
+        <v>-0.2344</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7403</v>
+        <v>-0.6758</v>
       </c>
       <c r="P17" t="n">
-        <v>1.0875</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R17" t="n">
-        <v>2.1751</v>
+        <v>0.87</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.9729</v>
+        <v>-1.1539</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.2209</v>
+        <v>-0.7667</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.752</v>
+        <v>-0.3873</v>
       </c>
       <c r="V17" t="n">
-        <v>1.3252</v>
+        <v>0.1745</v>
       </c>
       <c r="W17" t="n">
-        <v>1.3252</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.1745</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. TABOADA HEISKANEN</t>
+          <t>G. KANDE KIELI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6993</v>
+        <v>-0.3245</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7771</v>
+        <v>0.3752</v>
       </c>
       <c r="F18" t="n">
-        <v>0.07779999999999999</v>
+        <v>-0.6997</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.891</v>
+        <v>0.6556</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.891</v>
+        <v>0.4197</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>0.2359</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.7086</v>
+        <v>0.7633</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.7086</v>
+        <v>0.5721000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.1912</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1825</v>
+        <v>-0.1077</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1825</v>
+        <v>-0.1523</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>0.0446</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.9576</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.9576</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1918</v>
+        <v>-0.4825</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.3881</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2603</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-2.4552</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-2.4552</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. POWELL</t>
+          <t>C. TABOADA HEISKANEN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9546</v>
+        <v>-0.7108</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1263</v>
+        <v>-0.6653</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8283</v>
+        <v>-0.0455</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9295</v>
+        <v>-0.891</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.5383</v>
+        <v>-0.891</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4678</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1.8397</v>
+        <v>-0.7086</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.3039</v>
+        <v>-0.7086</v>
       </c>
       <c r="L19" t="n">
-        <v>2.1436</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9101</v>
+        <v>-0.1825</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2344</v>
+        <v>-0.1825</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6758</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.2175</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.87</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.8411</v>
+        <v>0.1803</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8784</v>
+        <v>0.0433</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.9627</v>
+        <v>0.137</v>
       </c>
       <c r="V19" t="n">
-        <v>0.1745</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.1745</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4838</v>
+        <v>-1.6945</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9693000000000001</v>
+        <v>0.5222</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.4531</v>
+        <v>-2.2167</v>
       </c>
       <c r="G20" t="n">
         <v>1.9706</v>
@@ -2014,13 +2014,13 @@
         <v>0.435</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4317</v>
+        <v>-0.6423</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0721</v>
+        <v>-0.3749</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5038</v>
+        <v>-0.2674</v>
       </c>
       <c r="V20" t="n">
         <v>-0.1952</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. RODRÍGUEZ RAMOS</t>
+          <t>D. VAN OOSTRUM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7046</v>
+        <v>-1.7471</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.0153</v>
+        <v>-1.8938</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3107</v>
+        <v>0.1467</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.9196</v>
+        <v>-1.4099</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.7459</v>
+        <v>-0.2282</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1737</v>
+        <v>-1.1817</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.862</v>
+        <v>-0.5756</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.3441</v>
+        <v>0.0547</v>
       </c>
       <c r="L21" t="n">
-        <v>0.4822</v>
+        <v>-0.6303</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.0576</v>
+        <v>-0.8344</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4018</v>
+        <v>-0.2829</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6558</v>
+        <v>-0.5514</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.9576</v>
+        <v>-0.435</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.3501</v>
+        <v>-1.0875</v>
       </c>
       <c r="R21" t="n">
-        <v>2.3926</v>
+        <v>0.6525</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2826</v>
+        <v>-0.2719</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2584</v>
+        <v>-0.2307</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0243</v>
+        <v>-0.0412</v>
       </c>
       <c r="V21" t="n">
-        <v>2.4552</v>
+        <v>0.3698</v>
       </c>
       <c r="W21" t="n">
-        <v>2.4552</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. VAN OOSTRUM</t>
+          <t>S. RODRÍGUEZ RAMOS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.0129</v>
+        <v>-2</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.0056</v>
+        <v>-3.2388</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0074</v>
+        <v>1.2388</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.4099</v>
+        <v>-1.9196</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.2282</v>
+        <v>-1.7459</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.1817</v>
+        <v>-0.1737</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.5756</v>
+        <v>-0.862</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0547</v>
+        <v>-1.3441</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6303</v>
+        <v>0.4822</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.8344</v>
+        <v>-1.0576</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2829</v>
+        <v>-0.4018</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.5514</v>
+        <v>-0.6558</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.435</v>
+        <v>-1.9576</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.0875</v>
+        <v>-4.3501</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6525</v>
+        <v>2.3926</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5377999999999999</v>
+        <v>-0.578</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3425</v>
+        <v>-0.4819</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1953</v>
+        <v>-0.0961</v>
       </c>
       <c r="V22" t="n">
-        <v>0.3698</v>
+        <v>2.4552</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.4552</v>
       </c>
       <c r="X22" t="n">
-        <v>0.3698</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.5365</v>
+        <v>-3.4041</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.5267</v>
+        <v>-2.4149</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.0098</v>
+        <v>-0.9892</v>
       </c>
       <c r="G23" t="n">
         <v>-3.1608</v>
@@ -2248,13 +2248,13 @@
         <v>0.6525</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0706</v>
+        <v>-0.9382</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6165</v>
+        <v>-0.5047</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4541</v>
+        <v>-0.4335</v>
       </c>
       <c r="V23" t="n">
         <v>1.13</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.6116</v>
+        <v>-3.5827</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3406</v>
+        <v>0.6758999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.9522</v>
+        <v>-4.2586</v>
       </c>
       <c r="G24" t="n">
         <v>-0.2959</v>
@@ -2326,13 +2326,13 @@
         <v>1.9576</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.4457</v>
+        <v>-1.4168</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8663999999999999</v>
+        <v>-0.5311</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.5793</v>
+        <v>-0.8857</v>
       </c>
       <c r="V24" t="n">
         <v>-0.5649999999999999</v>
@@ -2359,25 +2359,25 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-13.791</v>
+        <v>-11.5559</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.674899999999999</v>
+        <v>-5.6746</v>
       </c>
       <c r="F25" t="n">
-        <v>-8.116300000000001</v>
+        <v>-5.881200000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.4146</v>
+        <v>-2.414600000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.2473</v>
+        <v>-1.247299999999999</v>
       </c>
       <c r="I25" t="n">
         <v>-1.1674</v>
       </c>
       <c r="J25" t="n">
-        <v>5.0771</v>
+        <v>5.077099999999999</v>
       </c>
       <c r="K25" t="n">
         <v>1.5986</v>
@@ -2404,16 +2404,16 @@
         <v>13.0505</v>
       </c>
       <c r="S25" t="n">
-        <v>-9.223100000000001</v>
+        <v>-6.9878</v>
       </c>
       <c r="T25" t="n">
-        <v>-4.434299999999999</v>
+        <v>-4.4341</v>
       </c>
       <c r="U25" t="n">
-        <v>-4.7889</v>
+        <v>-2.5537</v>
       </c>
       <c r="V25" t="n">
-        <v>1.1093</v>
+        <v>1.109300000000001</v>
       </c>
       <c r="W25" t="n">
         <v>9.9953</v>
